--- a/XLibur.Tests/Resource/Examples/Styles/UsingRichText.xlsx
+++ b/XLibur.Tests/Resource/Examples/Styles/UsingRichText.xlsx
@@ -16,6 +16,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
+    <x:t>" BIG " is Bold.</x:t>
+  </x:si>
+  <x:si>
     <x:r>
       <x:rPr>
         <x:vertAlign val="baseline"/>
@@ -46,9 +49,6 @@
       </x:rPr>
       <x:t xml:space="preserve"> must go on...</x:t>
     </x:r>
-  </x:si>
-  <x:si>
-    <x:t>" BIG " is Bold.</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -592,7 +592,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -600,7 +600,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">

--- a/XLibur.Tests/Resource/Examples/Styles/UsingRichText.xlsx
+++ b/XLibur.Tests/Resource/Examples/Styles/UsingRichText.xlsx
@@ -580,14 +580,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:B6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="88.139196" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="35.853482" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="88.139196" customWidth="1"/>
+    <x:col min="2" max="2" width="35.853482" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2">
@@ -596,10 +593,10 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
-      <x:c r="A3" s="0" t="s">
+      <x:c r="A3" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
+      <x:c r="B3" t="s">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -607,7 +604,7 @@
       <x:c r="A5" s="2" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
+      <x:c r="B5" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -617,10 +614,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Examples/Styles/UsingRichText.xlsx
+++ b/XLibur.Tests/Resource/Examples/Styles/UsingRichText.xlsx
@@ -583,8 +583,8 @@
   <x:dimension ref="A1:B6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="88.139196" customWidth="1"/>
-    <x:col min="2" max="2" width="35.853482" customWidth="1"/>
+    <x:col min="1" max="1" width="86.139196" customWidth="1"/>
+    <x:col min="2" max="2" width="34.996339" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2">

--- a/XLibur.Tests/Resource/Examples/Styles/UsingRichText.xlsx
+++ b/XLibur.Tests/Resource/Examples/Styles/UsingRichText.xlsx
@@ -583,8 +583,8 @@
   <x:dimension ref="A1:B6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="86.139196" customWidth="1"/>
-    <x:col min="2" max="2" width="34.996339" customWidth="1"/>
+    <x:col min="1" max="1" width="86.142857" customWidth="1"/>
+    <x:col min="2" max="2" width="35" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2">
